--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00862B-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00862B-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A0ADA30-0903-499B-B00C-4B23C23135FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1ADBCEFB-CDD1-42EB-9B22-3328DF10B6A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{D90321CA-666A-488E-9EED-698F9943C8A5}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{5AF92F34-84C2-446C-9750-790DDE54647F}"/>
   </bookViews>
   <sheets>
     <sheet name="00862B-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1535,25 +1535,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3BBC29E-AB32-44FD-8AD3-5161C968B408}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06255E2A-7F40-4847-B467-245B81C42EB3}">
   <dimension ref="A1:R35"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.5" customWidth="1"/>
+    <col min="7" max="9" width="10" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1581,7 +1581,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1611,7 +1611,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1707,7 +1707,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1761,7 +1761,7 @@
         <v>4.88</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1817,7 +1817,7 @@
         <v>1.31</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>25</v>
       </c>
@@ -1929,7 +1929,7 @@
         <v>1.24</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>25</v>
       </c>
@@ -1985,7 +1985,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="39">
         <v>2024</v>
       </c>
@@ -2039,7 +2039,7 @@
         <v>4.88</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>25</v>
       </c>
@@ -2095,7 +2095,7 @@
         <v>1.21</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="17" t="s">
         <v>25</v>
       </c>
@@ -2151,7 +2151,7 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>25</v>
       </c>
@@ -2207,7 +2207,7 @@
         <v>1.26</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
         <v>25</v>
       </c>
@@ -2263,7 +2263,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="37">
         <v>2023</v>
       </c>
@@ -2317,7 +2317,7 @@
         <v>4.6500000000000004</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>25</v>
       </c>
@@ -2373,7 +2373,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>25</v>
       </c>
@@ -2429,7 +2429,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2485,7 +2485,7 @@
         <v>1.18</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2541,7 +2541,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2022</v>
       </c>
@@ -2595,7 +2595,7 @@
         <v>4.0199999999999996</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2707,7 +2707,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>25</v>
       </c>
@@ -2763,7 +2763,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>25</v>
       </c>
@@ -2819,7 +2819,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2021</v>
       </c>
@@ -2873,7 +2873,7 @@
         <v>2.73</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>25</v>
       </c>
@@ -2929,7 +2929,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>25</v>
       </c>
@@ -2985,7 +2985,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>25</v>
       </c>
@@ -3041,7 +3041,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>25</v>
       </c>
@@ -3097,7 +3097,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2020</v>
       </c>
@@ -3151,7 +3151,7 @@
         <v>3.25</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>25</v>
       </c>
@@ -3207,7 +3207,7 @@
         <v>0.76</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>25</v>
       </c>
@@ -3263,7 +3263,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>25</v>
       </c>
@@ -3319,7 +3319,7 @@
         <v>0.92</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
         <v>25</v>
       </c>
@@ -3375,7 +3375,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="37" t="s">
         <v>64</v>
       </c>
